--- a/temp_doc/pelamar_perusahaan.xlsx
+++ b/temp_doc/pelamar_perusahaan.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/jobfair_smkth/temp_doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29025B23-407C-4C46-90DE-B8C16F30FD70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73752917-29DF-1A44-833C-D9D40DDB14D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16440" xr2:uid="{98E99B6E-424B-5848-87EF-5E12535B1BF7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>id_pelamar_perusahaan </t>
   </si>
@@ -62,719 +62,29 @@
     <t>nama_perusahaan</t>
   </si>
   <si>
-    <t>Rafly zidan fadilla</t>
-  </si>
-  <si>
     <t>PRIA</t>
   </si>
   <si>
     <t>UMUM</t>
   </si>
   <si>
-    <t>Smk Remaja Pluit</t>
-  </si>
-  <si>
-    <t>JEFRI GIOVANIE</t>
-  </si>
-  <si>
-    <t>XII AKL 2</t>
-  </si>
-  <si>
-    <t>SMK TUNAS HARAPAN</t>
-  </si>
-  <si>
-    <t>Fauzi ghozali</t>
-  </si>
-  <si>
-    <t>Muhammad Rasya</t>
-  </si>
-  <si>
-    <t>XII PM</t>
-  </si>
-  <si>
-    <t>Melan Margareta Pare</t>
-  </si>
-  <si>
-    <t>Wanita</t>
-  </si>
-  <si>
-    <t>SMA STELLA MARIS</t>
-  </si>
-  <si>
-    <t>Vina puji Ristanti</t>
-  </si>
-  <si>
-    <t>SMK Al-Muttaqin</t>
-  </si>
-  <si>
-    <t>Ervan Hidayat</t>
-  </si>
-  <si>
-    <t>Mohamad Rizky Albiansyah</t>
-  </si>
-  <si>
-    <t>Zaky Raditya Susanta</t>
-  </si>
-  <si>
-    <t>YUDHA ADI WIJAYA</t>
-  </si>
-  <si>
-    <t>Muhammad Rizky</t>
-  </si>
-  <si>
-    <t>XII AKL 1</t>
-  </si>
-  <si>
-    <t>Tri Pramudya ramadhan</t>
-  </si>
-  <si>
-    <t>SMK media informatika</t>
-  </si>
-  <si>
-    <t>Azmil Muttaqin</t>
-  </si>
-  <si>
-    <t>SMK Al hamidiyah</t>
-  </si>
-  <si>
-    <t>Yeni Rahmayanti</t>
-  </si>
-  <si>
-    <t>Amelya</t>
-  </si>
-  <si>
-    <t>SMK Multimedia Mandiri</t>
-  </si>
-  <si>
-    <t>Nur Fitriah Ramadhani</t>
-  </si>
-  <si>
-    <t>JEFRI GIOVANNIE</t>
-  </si>
-  <si>
-    <t>AHMAD SHALEH SUBANDI</t>
-  </si>
-  <si>
-    <t>Madrasah Aliyah Asyrofuddin</t>
-  </si>
-  <si>
-    <t>Karmelia Putri</t>
-  </si>
-  <si>
-    <t>SMK PGRI 35 JAKARTA</t>
-  </si>
-  <si>
-    <t>NUR ADI PRASETYO</t>
-  </si>
-  <si>
-    <t>SMK METROPOLITAN CIKARANG</t>
-  </si>
-  <si>
-    <t>Ahmad Daffa Abiyu Anugrah</t>
-  </si>
-  <si>
-    <t>MA Aulia</t>
-  </si>
-  <si>
-    <t>Karmeliaa Putri</t>
-  </si>
-  <si>
-    <t>Desfianaputri widyarsanti</t>
-  </si>
-  <si>
-    <t>zaza nur anggraini</t>
-  </si>
-  <si>
-    <t>Irwansyah</t>
-  </si>
-  <si>
-    <t>NAUFAL SAPUTRA</t>
-  </si>
-  <si>
-    <t>SMKN 35 JAKARTA</t>
-  </si>
-  <si>
-    <t>Novi Wulandari</t>
-  </si>
-  <si>
-    <t>SMAN 84 JAKARTA BARAT</t>
-  </si>
-  <si>
-    <t>Dede Arum Sari</t>
-  </si>
-  <si>
-    <t>XII MPLB 1</t>
-  </si>
-  <si>
-    <t>Aryo tri wisnu</t>
-  </si>
-  <si>
-    <t>SMK PUTRA MANDIRI</t>
-  </si>
-  <si>
-    <t>Nur Awal Santoso</t>
-  </si>
-  <si>
-    <t>XII TJKT 2</t>
-  </si>
-  <si>
-    <t>Abdul Gani</t>
-  </si>
-  <si>
-    <t>Universitas Dian Nusantara</t>
-  </si>
-  <si>
-    <t>Nur Ishmatillah</t>
-  </si>
-  <si>
-    <t>Muhammad Fahmi Arasit</t>
-  </si>
-  <si>
-    <t>MAN 22 JAKARTA</t>
-  </si>
-  <si>
-    <t>Ibnu basunjay</t>
-  </si>
-  <si>
-    <t>XII TJKT 3</t>
-  </si>
-  <si>
-    <t>FASKALIS HAMBALLAH AKBAR</t>
-  </si>
-  <si>
-    <t>Melisa Pratiwi</t>
-  </si>
-  <si>
-    <t>SMA</t>
-  </si>
-  <si>
-    <t>Tisya Octavia Ramadhani</t>
-  </si>
-  <si>
-    <t>Annas Rasya Syaifulillah</t>
-  </si>
-  <si>
-    <t>SMK MA'ARIF NU JAKARTA</t>
-  </si>
-  <si>
-    <t>Retno Fauziah Hidayat</t>
-  </si>
-  <si>
-    <t>SMK Yapermas</t>
-  </si>
-  <si>
-    <t>ARDIANSYAH MULYA PRATAMA</t>
-  </si>
-  <si>
-    <t>SMAN 1 MUARA GEMBONG</t>
-  </si>
-  <si>
-    <t>ABDURROHMAN</t>
-  </si>
-  <si>
-    <t>Smk karya mandiri</t>
-  </si>
-  <si>
-    <t>Chika fitriyani</t>
-  </si>
-  <si>
-    <t>SMK Jakarta IV</t>
-  </si>
-  <si>
-    <t>ABDUL HAFID JAELANI</t>
-  </si>
-  <si>
-    <t>Wiyata Satya</t>
-  </si>
-  <si>
-    <t>RACHMAWATI</t>
-  </si>
-  <si>
-    <t>Smk assaadatul abadiyah</t>
-  </si>
-  <si>
-    <t>Muyko Aryanda</t>
-  </si>
-  <si>
-    <t>SMK YADIKA 2</t>
-  </si>
-  <si>
-    <t>Rama Herdiansyah</t>
-  </si>
-  <si>
-    <t>Muhammad zarkasyi</t>
-  </si>
-  <si>
-    <t>SMA NEGERI 1 KABANDUNGAN</t>
-  </si>
-  <si>
-    <t>Lukas Setia Atmaja</t>
-  </si>
-  <si>
-    <t>SMK PANCASILA 3 BATURETNO</t>
-  </si>
-  <si>
-    <t>Dhea Dwi Aryani</t>
-  </si>
-  <si>
-    <t>Singgih Umi Utami</t>
-  </si>
-  <si>
-    <t>Sma negeri 1 kabandungan</t>
-  </si>
-  <si>
-    <t>Khotibul Umam</t>
-  </si>
-  <si>
-    <t>SMA nur elfalah</t>
-  </si>
-  <si>
-    <t>Rahmat syarif</t>
-  </si>
-  <si>
-    <t>SMK PERWIRA JAKARTA</t>
-  </si>
-  <si>
-    <t>Mohammad Farhan</t>
-  </si>
-  <si>
-    <t>RYANK DIJAYANI PUTRA</t>
-  </si>
-  <si>
-    <t>SMK YADIKA2</t>
-  </si>
-  <si>
-    <t>Laras Anggraini</t>
-  </si>
-  <si>
-    <t>Universitas Satyagama</t>
-  </si>
-  <si>
-    <t>MUHAMMAD AGUNG NASRUL WATON</t>
-  </si>
-  <si>
-    <t>MA DARUSSALAM</t>
-  </si>
-  <si>
-    <t>Muhammad agung Nasrul waton</t>
-  </si>
-  <si>
-    <t>Muhammad Rizki Saputra</t>
-  </si>
-  <si>
-    <t>SMK Tunas Harapan</t>
-  </si>
-  <si>
-    <t>Nur Amalah</t>
-  </si>
-  <si>
-    <t>XII MPLB 2</t>
-  </si>
-  <si>
-    <t>SMK TUNAS HARAPAN JAKARTA BARAT</t>
-  </si>
-  <si>
-    <t>Diah Ayu Lestari</t>
-  </si>
-  <si>
-    <t>SMK Tunas Harapan Jakarta</t>
-  </si>
-  <si>
-    <t>Noreen triputra</t>
-  </si>
-  <si>
-    <t>SMK tunas harapan</t>
-  </si>
-  <si>
-    <t>Amelia Ananta Pratiwi</t>
-  </si>
-  <si>
-    <t>Muhamad fahrur rizqi</t>
-  </si>
-  <si>
-    <t>SMK PSKD3</t>
-  </si>
-  <si>
-    <t>Daviq Khalik</t>
-  </si>
-  <si>
-    <t>Tunas Harapan</t>
-  </si>
-  <si>
-    <t>Dimas Williamsyah</t>
-  </si>
-  <si>
-    <t>SMK PGRI 5 Jakarta</t>
-  </si>
-  <si>
-    <t>Eko Prasetyo</t>
-  </si>
-  <si>
-    <t>Nurma Hetty</t>
-  </si>
-  <si>
-    <t>Universitas terbuka jakarta</t>
-  </si>
-  <si>
-    <t>Nurma Hetty Hasugian</t>
-  </si>
-  <si>
-    <t>SITI SUHAENI AMALIYA</t>
-  </si>
-  <si>
-    <t>SMK Al Anshor</t>
-  </si>
-  <si>
-    <t>Putri lestari</t>
-  </si>
-  <si>
-    <t>SMK DEWI SARTIKA</t>
-  </si>
-  <si>
-    <t>Irma Yunita</t>
-  </si>
-  <si>
-    <t>SMK DEWI SARTIKA JAKARTA BARAT</t>
-  </si>
-  <si>
-    <t>Safira zahra</t>
-  </si>
-  <si>
-    <t>Muhamad Subastian</t>
-  </si>
-  <si>
-    <t>XII TJKT 1</t>
-  </si>
-  <si>
-    <t>Dina Auliani</t>
-  </si>
-  <si>
-    <t>SMA Tunas Harapan</t>
-  </si>
-  <si>
-    <t>RINI</t>
-  </si>
-  <si>
-    <t>Arya Nurkholik</t>
-  </si>
-  <si>
-    <t>Bayu Saputra</t>
-  </si>
-  <si>
-    <t>RIFKY NUR CAHYO</t>
-  </si>
-  <si>
-    <t>SMK Duta Mas</t>
-  </si>
-  <si>
-    <t>MUHAMAD IQBAL FADILLAH</t>
-  </si>
-  <si>
-    <t>SMK NEGERI 9 JAKARTA</t>
-  </si>
-  <si>
-    <t>Anis karsella</t>
-  </si>
-  <si>
-    <t>Vadia Nur Eka Putri</t>
-  </si>
-  <si>
-    <t>Madrasah Aliyah Al Aulia bogor</t>
-  </si>
-  <si>
-    <t>Krisna Anggara</t>
-  </si>
-  <si>
-    <t>0881012879288</t>
-  </si>
-  <si>
-    <t>082110919723</t>
-  </si>
-  <si>
-    <t>08815351279</t>
-  </si>
-  <si>
-    <t>085883121027</t>
-  </si>
-  <si>
-    <t>08889144606</t>
-  </si>
-  <si>
-    <t>085692596281</t>
-  </si>
-  <si>
-    <t>088292088507</t>
-  </si>
-  <si>
-    <t>085886862350</t>
-  </si>
-  <si>
-    <t>08119227708</t>
-  </si>
-  <si>
-    <t>083169817885</t>
-  </si>
-  <si>
-    <t>085780495346</t>
-  </si>
-  <si>
-    <t>085773017754</t>
-  </si>
-  <si>
-    <t>081315363193</t>
-  </si>
-  <si>
-    <t>08998405529</t>
-  </si>
-  <si>
-    <t>087726940144</t>
-  </si>
-  <si>
-    <t>081319873916</t>
-  </si>
-  <si>
-    <t>082298296321</t>
-  </si>
-  <si>
-    <t>085714887334</t>
-  </si>
-  <si>
-    <t>0881037039030</t>
-  </si>
-  <si>
-    <t>085891112073</t>
-  </si>
-  <si>
-    <t>082297159944</t>
-  </si>
-  <si>
-    <t>085211170798</t>
-  </si>
-  <si>
-    <t>085811568819</t>
-  </si>
-  <si>
-    <t>082249685783</t>
-  </si>
-  <si>
-    <t>082249685793</t>
-  </si>
-  <si>
-    <t>085780086387</t>
-  </si>
-  <si>
-    <t>0881012175136</t>
-  </si>
-  <si>
-    <t>083826724082</t>
-  </si>
-  <si>
-    <t>089517483578</t>
-  </si>
-  <si>
-    <t>081389697701</t>
-  </si>
-  <si>
-    <t>081818716000</t>
-  </si>
-  <si>
-    <t>085211616556</t>
-  </si>
-  <si>
-    <t>08998491585</t>
-  </si>
-  <si>
-    <t>085117816164</t>
-  </si>
-  <si>
-    <t>089527458464</t>
-  </si>
-  <si>
-    <t>0881012833523</t>
-  </si>
-  <si>
-    <t>085772537515</t>
-  </si>
-  <si>
-    <t>082113887506</t>
-  </si>
-  <si>
-    <t>085950385298</t>
-  </si>
-  <si>
-    <t>085810450681</t>
-  </si>
-  <si>
-    <t>083874817307</t>
-  </si>
-  <si>
-    <t>085779248603</t>
-  </si>
-  <si>
-    <t>0895425410899</t>
-  </si>
-  <si>
-    <t>085770080109</t>
-  </si>
-  <si>
-    <t>087827714869</t>
-  </si>
-  <si>
-    <t>085888639631</t>
-  </si>
-  <si>
-    <t>085283443359</t>
-  </si>
-  <si>
-    <t>089530939385</t>
-  </si>
-  <si>
-    <t>082246397524</t>
-  </si>
-  <si>
-    <t>0895321031349</t>
-  </si>
-  <si>
-    <t>083143045781</t>
-  </si>
-  <si>
-    <t>089654729051</t>
-  </si>
-  <si>
-    <t>089655835767</t>
-  </si>
-  <si>
-    <t>085811333771</t>
-  </si>
-  <si>
-    <t>0895414735752</t>
-  </si>
-  <si>
-    <t>085814627184</t>
-  </si>
-  <si>
-    <t>088213126394</t>
-  </si>
-  <si>
-    <t>085150563574</t>
-  </si>
-  <si>
-    <t>085172279318</t>
-  </si>
-  <si>
-    <t>085782739068</t>
-  </si>
-  <si>
-    <t>081213369835</t>
-  </si>
-  <si>
-    <t>083830106107</t>
-  </si>
-  <si>
-    <t>085212917741</t>
-  </si>
-  <si>
-    <t>088291052293</t>
-  </si>
-  <si>
-    <t>081774865647</t>
-  </si>
-  <si>
-    <t>088293116313</t>
-  </si>
-  <si>
-    <t>083874043787</t>
-  </si>
-  <si>
-    <t>083870279373</t>
-  </si>
-  <si>
-    <t>085772541696</t>
-  </si>
-  <si>
-    <t>085150563560</t>
-  </si>
-  <si>
-    <t>081882826854</t>
-  </si>
-  <si>
-    <t>089630148182</t>
-  </si>
-  <si>
-    <t>085842963990</t>
-  </si>
-  <si>
-    <t>085714379563</t>
-  </si>
-  <si>
-    <t>085931284555</t>
-  </si>
-  <si>
-    <t>087777165186</t>
-  </si>
-  <si>
-    <t>085817135722</t>
-  </si>
-  <si>
-    <t>089507875661</t>
-  </si>
-  <si>
-    <t>088210498041</t>
-  </si>
-  <si>
-    <t>085779691175</t>
-  </si>
-  <si>
-    <t>LPK UNIVERSAL LANGUAGE SKILLS</t>
-  </si>
-  <si>
-    <t>PT SUMBER BINTANG PERKASA</t>
-  </si>
-  <si>
-    <t>KAWAN LAMA GROUP (AZKO)</t>
-  </si>
-  <si>
-    <t>PT INTI PRIMA KARYA</t>
-  </si>
-  <si>
-    <t>PT SUKSESINDO</t>
-  </si>
-  <si>
     <t>PT SUMBER ALFARIA TRIJAYA TBK</t>
   </si>
   <si>
-    <t>PT BREXA RAYA INDONESIA</t>
+    <t>ACHMAD IQBAL MAULANA</t>
   </si>
   <si>
-    <t>PT PENDEKAR BODOH (DCOST SEAFOOD)</t>
+    <t>SMK REMAJA PLUIT</t>
   </si>
   <si>
-    <t>PT SCORE TAX TEKNOLOGI INDONESIA</t>
-  </si>
-  <si>
-    <t>PT PRIMA FAJAR CAHAYA SURYA</t>
-  </si>
-  <si>
-    <t>MARTHA TILAAR SPA (PT CANTIKA PUSPAPESONA)</t>
-  </si>
-  <si>
-    <t>PT BERCA HARDAYAPERKASA</t>
-  </si>
-  <si>
-    <t>PT EGA TEKELINDO PRIMA</t>
-  </si>
-  <si>
-    <t>PT WIJAYA MACHINE PERKASA</t>
-  </si>
-  <si>
-    <t>Kalisa nabila</t>
+    <t>081382654090</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -791,6 +101,12 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="25"/>
+      <color rgb="FF030F19"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -815,11 +131,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7953,2655 +7272,939 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>1001</v>
+        <v>1110</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="2">
+        <v>2022</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1">
-        <v>2024</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>229</v>
-      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>1002</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="1">
-        <v>2025</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>230</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>1003</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="1">
-        <v>2025</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>230</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>1004</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="1">
-        <v>2025</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>231</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>1005</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="2">
-        <v>2027</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>232</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>1006</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>233</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>1007</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>234</v>
-      </c>
+      <c r="A8" s="1"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>1008</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>230</v>
-      </c>
+      <c r="A9" s="1"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>1009</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>230</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>1010</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>234</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <v>1011</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="2">
-        <v>2022</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>231</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
-        <v>1012</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>235</v>
-      </c>
+      <c r="A13" s="1"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
-        <v>1013</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>234</v>
-      </c>
+      <c r="A14" s="1"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
-        <v>1014</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>231</v>
-      </c>
+      <c r="A15" s="1"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
-        <v>1015</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="1">
-        <v>2023</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>236</v>
-      </c>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
-        <v>1016</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>236</v>
-      </c>
+      <c r="A17" s="1"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
-        <v>1017</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
-        <v>1018</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>231</v>
-      </c>
+      <c r="A18" s="1"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" ht="31" x14ac:dyDescent="0.3">
+      <c r="A19" s="1"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
-        <v>1019</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="1">
-        <v>2025</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>236</v>
-      </c>
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
-        <v>1020</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>230</v>
-      </c>
+      <c r="A21" s="1"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
-        <v>1021</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="2">
-        <v>2019</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>230</v>
-      </c>
+      <c r="A22" s="1"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
-        <v>1022</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="1">
-        <v>2022</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>234</v>
-      </c>
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="1">
-        <v>1023</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="1">
-        <v>2023</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>234</v>
-      </c>
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
-        <v>1024</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="1">
-        <v>2025</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>236</v>
-      </c>
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <v>1025</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="1">
-        <v>2024</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>231</v>
-      </c>
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
-        <v>1026</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" s="1">
-        <v>2022</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>236</v>
-      </c>
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="1">
-        <v>1027</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" s="2">
-        <v>2022</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>236</v>
-      </c>
+      <c r="A28" s="1"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="1">
-        <v>1028</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E29" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>236</v>
-      </c>
+      <c r="A29" s="1"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
-        <v>1029</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E30" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>231</v>
-      </c>
+      <c r="A30" s="1"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="1">
-        <v>1030</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>234</v>
-      </c>
+      <c r="A31" s="1"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="1">
-        <v>1031</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E32" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>234</v>
-      </c>
+      <c r="A32" s="1"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="1">
-        <v>1032</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>234</v>
-      </c>
+      <c r="A33" s="1"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="1">
-        <v>1033</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>237</v>
-      </c>
+      <c r="A34" s="1"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="1">
-        <v>1034</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>238</v>
-      </c>
+      <c r="A35" s="1"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="1">
-        <v>1035</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E36" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>236</v>
-      </c>
+      <c r="A36" s="1"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="1">
-        <v>1036</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>231</v>
-      </c>
+      <c r="A37" s="1"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="1">
-        <v>1037</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E38" s="2">
-        <v>2022</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>233</v>
-      </c>
+      <c r="A38" s="1"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="1">
-        <v>1038</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" s="1">
-        <v>2022</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>233</v>
-      </c>
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="1">
-        <v>1039</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E40" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>233</v>
-      </c>
+      <c r="A40" s="1"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="1">
-        <v>1040</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>231</v>
-      </c>
+      <c r="A41" s="1"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="1">
-        <v>1041</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>231</v>
-      </c>
+      <c r="A42" s="1"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="1">
-        <v>1042</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" s="2">
-        <v>2021</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>231</v>
-      </c>
+      <c r="A43" s="1"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="1">
-        <v>1043</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E44" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>235</v>
-      </c>
+      <c r="A44" s="1"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="1">
-        <v>1044</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E45" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>233</v>
-      </c>
+      <c r="A45" s="1"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="1">
-        <v>1045</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E46" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>233</v>
-      </c>
+      <c r="A46" s="1"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" s="1">
-        <v>1046</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E47" s="1">
-        <v>2023</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>239</v>
-      </c>
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="1">
-        <v>1047</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" s="1">
-        <v>2025</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>234</v>
-      </c>
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="1">
-        <v>1048</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E49" s="1">
-        <v>2023</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>229</v>
-      </c>
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" s="1">
-        <v>1049</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E50" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>234</v>
-      </c>
+      <c r="A50" s="1"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" s="1">
-        <v>1050</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>233</v>
-      </c>
+      <c r="A51" s="1"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" s="1">
-        <v>1051</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E52" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>231</v>
-      </c>
+      <c r="A52" s="1"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A53" s="1">
-        <v>1052</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>233</v>
-      </c>
+      <c r="A53" s="1"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" s="1">
-        <v>1053</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E54" s="2">
-        <v>2018</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>234</v>
-      </c>
+      <c r="A54" s="1"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A55" s="1">
-        <v>1054</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E55" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>234</v>
-      </c>
+      <c r="A55" s="1"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" s="1">
-        <v>1055</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E56" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>231</v>
-      </c>
+      <c r="A56" s="1"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" s="1">
-        <v>1056</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E57" s="2">
-        <v>2009</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>231</v>
-      </c>
+      <c r="A57" s="1"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" s="1">
-        <v>1057</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E58" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>237</v>
-      </c>
+      <c r="A58" s="1"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" s="1">
-        <v>1058</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E59" s="2">
-        <v>2021</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>234</v>
-      </c>
+      <c r="A59" s="1"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" s="1">
-        <v>1059</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E60" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>236</v>
-      </c>
+      <c r="A60" s="1"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" s="1">
-        <v>1060</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E61" s="1">
-        <v>2021</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>235</v>
-      </c>
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62" s="1">
-        <v>1061</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E62" s="1">
-        <v>2025</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>236</v>
-      </c>
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" s="1">
-        <v>1062</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E63" s="1">
-        <v>2025</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>234</v>
-      </c>
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" s="1">
-        <v>1063</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E64" s="1">
-        <v>2023</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>231</v>
-      </c>
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A65" s="1">
-        <v>1064</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E65" s="1">
-        <v>2026</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>230</v>
-      </c>
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A66" s="1">
-        <v>1065</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E66" s="1">
-        <v>2007</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>236</v>
-      </c>
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A67" s="1">
-        <v>1066</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E67" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>240</v>
-      </c>
+      <c r="A67" s="1"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A68" s="1">
-        <v>1067</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E68" s="2">
-        <v>2016</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>234</v>
-      </c>
+      <c r="A68" s="1"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A69" s="1">
-        <v>1068</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E69" s="2">
-        <v>2019</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>234</v>
-      </c>
+      <c r="A69" s="1"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A70" s="1">
-        <v>1069</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E70" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>234</v>
-      </c>
+      <c r="A70" s="1"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A71" s="1">
-        <v>1070</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E71" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>234</v>
-      </c>
+      <c r="A71" s="1"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A72" s="1">
-        <v>1071</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E72" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>236</v>
-      </c>
+      <c r="A72" s="1"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A73" s="1">
-        <v>1072</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E73" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>234</v>
-      </c>
+      <c r="A73" s="1"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A74" s="1">
-        <v>1073</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E74" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>234</v>
-      </c>
+      <c r="A74" s="1"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A75" s="1">
-        <v>1074</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E75" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>234</v>
-      </c>
+      <c r="A75" s="1"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A76" s="1">
-        <v>1075</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E76" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>234</v>
-      </c>
+      <c r="A76" s="1"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A77" s="1">
-        <v>1076</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E77" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>241</v>
-      </c>
+      <c r="A77" s="1"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A78" s="1">
-        <v>1077</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E78" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>233</v>
-      </c>
+      <c r="A78" s="1"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A79" s="1">
-        <v>1078</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E79" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>242</v>
-      </c>
+      <c r="A79" s="1"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A80" s="1">
-        <v>1079</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E80" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>234</v>
-      </c>
+      <c r="A80" s="1"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A81" s="1">
-        <v>1080</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E81" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>230</v>
-      </c>
+      <c r="A81" s="1"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A82" s="1">
-        <v>1081</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E82" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>231</v>
-      </c>
+      <c r="A82" s="1"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A83" s="1">
-        <v>1082</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E83" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>234</v>
-      </c>
+      <c r="A83" s="1"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A84" s="1">
-        <v>1083</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E84" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>233</v>
-      </c>
+      <c r="A84" s="1"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A85" s="1">
-        <v>1084</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E85" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>238</v>
-      </c>
+      <c r="A85" s="1"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A86" s="1">
-        <v>1085</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E86" s="2">
-        <v>2022</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>234</v>
-      </c>
+      <c r="A86" s="1"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A87" s="1">
-        <v>1086</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E87" s="2">
-        <v>2019</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>236</v>
-      </c>
+      <c r="A87" s="1"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A88" s="1">
-        <v>1087</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E88" s="2">
-        <v>2018</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>236</v>
-      </c>
+      <c r="A88" s="1"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A89" s="1">
-        <v>1088</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E89" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>231</v>
-      </c>
+      <c r="A89" s="1"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A90" s="1">
-        <v>1089</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E90" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>235</v>
-      </c>
+      <c r="A90" s="1"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A91" s="1">
-        <v>1090</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E91" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>233</v>
-      </c>
+      <c r="A91" s="1"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A92" s="1">
-        <v>1091</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E92" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>236</v>
-      </c>
+      <c r="A92" s="1"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A93" s="1">
-        <v>1092</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E93" s="2">
-        <v>2005</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>232</v>
-      </c>
+      <c r="A93" s="1"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A94" s="1">
-        <v>1093</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E94" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>231</v>
-      </c>
+      <c r="A94" s="1"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A95" s="1">
-        <v>1094</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E95" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>235</v>
-      </c>
+      <c r="A95" s="1"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A96" s="1">
-        <v>1095</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E96" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>233</v>
-      </c>
+      <c r="A96" s="1"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A97" s="1">
-        <v>1096</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E97" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>241</v>
-      </c>
+      <c r="A97" s="1"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A98" s="1">
-        <v>1097</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E98" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>234</v>
-      </c>
+      <c r="A98" s="1"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A99" s="1">
-        <v>1098</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E99" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>231</v>
-      </c>
+      <c r="A99" s="1"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A100" s="1">
-        <v>1099</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E100" s="2">
-        <v>2022</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>230</v>
-      </c>
+      <c r="A100" s="1"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A101" s="1">
-        <v>1100</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E101" s="2">
-        <v>2019</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>233</v>
-      </c>
+      <c r="A101" s="1"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A102" s="1">
-        <v>1101</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E102" s="2">
-        <v>2019</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>236</v>
-      </c>
+      <c r="A102" s="1"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A103" s="1">
-        <v>1102</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E103" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F103" s="2">
-        <v>85771607409</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>230</v>
-      </c>
+      <c r="A103" s="1"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
